--- a/tools/importer/reports/import-marketing-landing.report.xlsx
+++ b/tools/importer/reports/import-marketing-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="118">
   <si>
     <t>_reportFile</t>
   </si>
@@ -58,6 +58,66 @@
     <t>https://www.intel.com/content/www/us/en/homepage.html</t>
   </si>
   <si>
+    <t>support.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","cards-news"]</t>
+  </si>
+  <si>
+    <t>support</t>
+  </si>
+  <si>
+    <t>institutional-landing</t>
+  </si>
+  <si>
+    <t>2026-04-01T20:31:44.366Z</t>
+  </si>
+  <si>
+    <t>Intel Support</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/support.html</t>
+  </si>
+  <si>
+    <t>ai-pc/overview.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","cards-product","cards-product","cards-product","cards-product","columns","columns","columns","cards-resource"]</t>
+  </si>
+  <si>
+    <t>ai-pc/overview</t>
+  </si>
+  <si>
+    <t>marketing-landing</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:16.627Z</t>
+  </si>
+  <si>
+    <t>The AI PC Powered by Intel. Now AI Is for Everyone</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/ai-pc/overview.html</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/analytics.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-product","cards-product","cards-product","cards-resource"]</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/analytics</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:48.245Z</t>
+  </si>
+  <si>
+    <t>Advanced Analytics Solutions – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/artificial-intelligence/analytics.html</t>
+  </si>
+  <si>
     <t>artificial-intelligence/overview.report.json</t>
   </si>
   <si>
@@ -67,9 +127,6 @@
     <t>artificial-intelligence/overview</t>
   </si>
   <si>
-    <t>marketing-landing</t>
-  </si>
-  <si>
     <t>2026-04-01T19:51:32.419Z</t>
   </si>
   <si>
@@ -79,6 +136,153 @@
     <t>https://www.intel.com/content/www/us/en/artificial-intelligence/overview.html</t>
   </si>
   <si>
+    <t>artificial-intelligence/processors.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","cards-product","cards-product","columns","columns","columns"]</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/processors</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:23.438Z</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence (AI) Processors – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/artificial-intelligence/processors.html</t>
+  </si>
+  <si>
+    <t>corporate-responsibility/corporate-responsibility.report.json</t>
+  </si>
+  <si>
+    <t>["cards-news","cards-news","cards-news","cards-news","cards-news","cards-news","cards-news","cards-news","cards-news"]</t>
+  </si>
+  <si>
+    <t>corporate-responsibility/corporate-responsibility</t>
+  </si>
+  <si>
+    <t>2026-04-01T20:31:49.007Z</t>
+  </si>
+  <si>
+    <t>Corporate Social Responsibility</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/corporate-responsibility/corporate-responsibility.html</t>
+  </si>
+  <si>
+    <t>developer/overview.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>developer/overview</t>
+  </si>
+  <si>
+    <t>category-directory</t>
+  </si>
+  <si>
+    <t>2026-04-01T20:26:18.055Z</t>
+  </si>
+  <si>
+    <t>Intel Developer Zone</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/overview.html</t>
+  </si>
+  <si>
+    <t>edge-computing/overview.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","cards-product","columns","columns","retailer-locator","retailer-locator","retailer-locator","retailer-locator","cards-resource"]</t>
+  </si>
+  <si>
+    <t>edge-computing/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:36.863Z</t>
+  </si>
+  <si>
+    <t>Edge Computing Solutions – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/edge-computing/overview.html</t>
+  </si>
+  <si>
+    <t>environment/sustainability.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-product","cards-product","cards-product","cards-product","retailer-locator"]</t>
+  </si>
+  <si>
+    <t>environment/sustainability</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:58.658Z</t>
+  </si>
+  <si>
+    <t>Sustainable Computing for a Sustainable Future</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/environment/sustainability.html</t>
+  </si>
+  <si>
+    <t>gaming/esports.report.json</t>
+  </si>
+  <si>
+    <t>["hero"]</t>
+  </si>
+  <si>
+    <t>gaming/esports</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:09.629Z</t>
+  </si>
+  <si>
+    <t>Esports: Transforming the Future of Gaming Technology - Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/gaming/esports.html</t>
+  </si>
+  <si>
+    <t>gaming/gaming-desktops.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-product","cards-product","cards-product","cards-product","cards-product","columns","columns","columns","columns","retailer-locator","retailer-locator","cards-resource"]</t>
+  </si>
+  <si>
+    <t>gaming/gaming-desktops</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:57:56.946Z</t>
+  </si>
+  <si>
+    <t>Gaming Desktops Powered by Intel Core Ultra 200S Plus</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/gaming/gaming-desktops.html</t>
+  </si>
+  <si>
+    <t>gaming/gaming-laptops.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-resource"]</t>
+  </si>
+  <si>
+    <t>gaming/gaming-laptops</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:02.540Z</t>
+  </si>
+  <si>
+    <t>Gaming Laptops Powered by Intel® Core Ultra Series 2</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/gaming/gaming-laptops.html</t>
+  </si>
+  <si>
     <t>gaming/serious-gaming.report.json</t>
   </si>
   <si>
@@ -95,6 +299,72 @@
   </si>
   <si>
     <t>https://www.intel.com/content/www/us/en/gaming/serious-gaming.html</t>
+  </si>
+  <si>
+    <t>manufacturing/manufacturing-industrial-overview.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","cards-product","cards-product","cards-product","cards-product","columns","columns"]</t>
+  </si>
+  <si>
+    <t>manufacturing/manufacturing-industrial-overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:53.206Z</t>
+  </si>
+  <si>
+    <t>Industry 4.0 and Smart Manufacturing Technology Solutions Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/manufacturing/manufacturing-industrial-overview.html</t>
+  </si>
+  <si>
+    <t>products/overview.report.json</t>
+  </si>
+  <si>
+    <t>products/overview</t>
+  </si>
+  <si>
+    <t>2026-04-01T20:26:11.962Z</t>
+  </si>
+  <si>
+    <t>Intel® Core™ Processors, FPGAs, GPUs, Networking, Software</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/products/overview.html</t>
+  </si>
+  <si>
+    <t>products/details/processors/core-ultra.report.json</t>
+  </si>
+  <si>
+    <t>products/details/processors/core-ultra</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:29.188Z</t>
+  </si>
+  <si>
+    <t>New Intel® Core™ Ultra Series 3 Processors</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/products/details/processors/core-ultra.html</t>
+  </si>
+  <si>
+    <t>products/docs/discrete-gpus/arc/desktop/b-series/overview.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","columns","columns","columns","columns","cards-resource"]</t>
+  </si>
+  <si>
+    <t>products/docs/discrete-gpus/arc/desktop/b-series/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:58:42.572Z</t>
+  </si>
+  <si>
+    <t>Intel® Arc™ B-Series Graphics for Desktops</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/products/docs/discrete-gpus/arc/desktop/b-series/overview.html</t>
   </si>
 </sst>
 </file>
@@ -483,13 +753,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
@@ -586,16 +854,406 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
         <v>25</v>
       </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-marketing-landing.report.xlsx
+++ b/tools/importer/reports/import-marketing-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="173">
   <si>
     <t>_reportFile</t>
   </si>
@@ -127,7 +127,7 @@
     <t>artificial-intelligence/overview</t>
   </si>
   <si>
-    <t>2026-04-01T19:51:32.419Z</t>
+    <t>2026-04-04T17:46:47.943Z</t>
   </si>
   <si>
     <t>Explore Intel® Artificial Intelligence Solutions</t>
@@ -154,6 +154,57 @@
     <t>https://www.intel.com/content/www/us/en/artificial-intelligence/processors.html</t>
   </si>
   <si>
+    <t>artificial-intelligence/responsible-ai.report.json</t>
+  </si>
+  <si>
+    <t>artificial-intelligence/responsible-ai</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:01:14.288Z</t>
+  </si>
+  <si>
+    <t>Responsible AI</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/artificial-intelligence/responsible-ai.html</t>
+  </si>
+  <si>
+    <t>cloud-computing/overview.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>cloud-computing/overview</t>
+  </si>
+  <si>
+    <t>category-directory</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:00:06.719Z</t>
+  </si>
+  <si>
+    <t>Cloud Computing Solutions – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/cloud-computing/overview.html</t>
+  </si>
+  <si>
+    <t>company-overview/company-overview.report.json</t>
+  </si>
+  <si>
+    <t>company-overview/company-overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:01:07.254Z</t>
+  </si>
+  <si>
+    <t>Innovation starts here</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/company-overview/company-overview.html</t>
+  </si>
+  <si>
     <t>corporate-responsibility/corporate-responsibility.report.json</t>
   </si>
   <si>
@@ -172,18 +223,27 @@
     <t>https://www.intel.com/content/www/us/en/corporate-responsibility/corporate-responsibility.html</t>
   </si>
   <si>
+    <t>data-center/overview.report.json</t>
+  </si>
+  <si>
+    <t>data-center/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:00:13.072Z</t>
+  </si>
+  <si>
+    <t>Data Center Solutions – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/data-center/overview.html</t>
+  </si>
+  <si>
     <t>developer/overview.report.json</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
     <t>developer/overview</t>
   </si>
   <si>
-    <t>category-directory</t>
-  </si>
-  <si>
     <t>2026-04-01T20:26:18.055Z</t>
   </si>
   <si>
@@ -292,7 +352,7 @@
     <t>gaming/serious-gaming</t>
   </si>
   <si>
-    <t>2026-04-01T19:51:26.791Z</t>
+    <t>2026-04-04T17:46:43.880Z</t>
   </si>
   <si>
     <t>Next‑Gen Gaming PCs Powered by Intel® Core™ Ultra Series 2</t>
@@ -301,6 +361,21 @@
     <t>https://www.intel.com/content/www/us/en/gaming/serious-gaming.html</t>
   </si>
   <si>
+    <t>high-performance-computing/overview.report.json</t>
+  </si>
+  <si>
+    <t>high-performance-computing/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:00:23.027Z</t>
+  </si>
+  <si>
+    <t>High Performance Computing (HPC) Solutions - Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/high-performance-computing/overview.html</t>
+  </si>
+  <si>
     <t>manufacturing/manufacturing-industrial-overview.report.json</t>
   </si>
   <si>
@@ -332,6 +407,96 @@
   </si>
   <si>
     <t>https://www.intel.com/content/www/us/en/products/overview.html</t>
+  </si>
+  <si>
+    <t>security/overview.report.json</t>
+  </si>
+  <si>
+    <t>security/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:00:17.973Z</t>
+  </si>
+  <si>
+    <t>Security Innovation for Business Networks | Intel®</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/security/overview.html</t>
+  </si>
+  <si>
+    <t>topics/overview.report.json</t>
+  </si>
+  <si>
+    <t>topics/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T21:00:01.146Z</t>
+  </si>
+  <si>
+    <t>Topics</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/topics/overview.html</t>
+  </si>
+  <si>
+    <t>developer/programs/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/programs/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:59:56.695Z</t>
+  </si>
+  <si>
+    <t>Developer Programs from Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/programs/overview.html</t>
+  </si>
+  <si>
+    <t>developer/tools/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/tools/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:59:51.171Z</t>
+  </si>
+  <si>
+    <t>Development Tools</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/tools/overview.html</t>
+  </si>
+  <si>
+    <t>developer/topic-technology/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/topic-technology/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:59:46.073Z</t>
+  </si>
+  <si>
+    <t>Development Technologies</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/topic-technology/overview.html</t>
+  </si>
+  <si>
+    <t>gaming/resources/overview.report.json</t>
+  </si>
+  <si>
+    <t>gaming/resources/overview</t>
+  </si>
+  <si>
+    <t>2026-04-03T20:59:41.422Z</t>
+  </si>
+  <si>
+    <t>Intel® Gaming-Technik und -Produkte – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/gaming/resources/overview.html</t>
   </si>
   <si>
     <t>products/details/processors/core-ultra.report.json</t>
@@ -753,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -949,10 +1114,10 @@
         <v>47</v>
       </c>
       <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
         <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -961,154 +1126,154 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
         <v>50</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>51</v>
-      </c>
-      <c r="H8" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
         <v>55</v>
       </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>56</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>57</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>58</v>
-      </c>
-      <c r="H9" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
         <v>61</v>
       </c>
-      <c r="C10" t="s">
+      <c r="G10" t="s">
         <v>62</v>
       </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>63</v>
-      </c>
-      <c r="G10" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
         <v>66</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
         <v>67</v>
       </c>
-      <c r="C11" t="s">
+      <c r="G11" t="s">
         <v>68</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>69</v>
-      </c>
-      <c r="G11" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" t="s">
         <v>72</v>
       </c>
-      <c r="B12" t="s">
+      <c r="G12" t="s">
         <v>73</v>
       </c>
-      <c r="C12" t="s">
+      <c r="H12" t="s">
         <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" t="s">
-        <v>76</v>
-      </c>
-      <c r="H12" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
         <v>78</v>
       </c>
-      <c r="B13" t="s">
+      <c r="H13" t="s">
         <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -1117,24 +1282,24 @@
         <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
@@ -1143,24 +1308,24 @@
         <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1169,50 +1334,50 @@
         <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G16" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H16" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" t="s">
         <v>102</v>
       </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="H17" t="s">
         <v>103</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1221,24 +1386,24 @@
         <v>25</v>
       </c>
       <c r="F18" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H18" t="s">
         <v>109</v>
-      </c>
-      <c r="G18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
         <v>112</v>
-      </c>
-      <c r="B19" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" t="s">
-        <v>114</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1247,13 +1412,299 @@
         <v>25</v>
       </c>
       <c r="F19" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" t="s">
         <v>115</v>
       </c>
-      <c r="G19" t="s">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>116</v>
       </c>
-      <c r="H19" t="s">
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
         <v>117</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" t="s">
+        <v>125</v>
+      </c>
+      <c r="H21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" t="s">
+        <v>139</v>
+      </c>
+      <c r="G24" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" t="s">
+        <v>145</v>
+      </c>
+      <c r="H25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" t="s">
+        <v>149</v>
+      </c>
+      <c r="G26" t="s">
+        <v>150</v>
+      </c>
+      <c r="H26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" t="s">
+        <v>154</v>
+      </c>
+      <c r="G27" t="s">
+        <v>155</v>
+      </c>
+      <c r="H27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" t="s">
+        <v>159</v>
+      </c>
+      <c r="G28" t="s">
+        <v>160</v>
+      </c>
+      <c r="H28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" t="s">
+        <v>163</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>164</v>
+      </c>
+      <c r="G29" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>167</v>
+      </c>
+      <c r="B30" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" t="s">
+        <v>169</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>170</v>
+      </c>
+      <c r="G30" t="s">
+        <v>171</v>
+      </c>
+      <c r="H30" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-marketing-landing.report.xlsx
+++ b/tools/importer/reports/import-marketing-landing.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-04-01T18:39:19.586Z</t>
+    <t>2026-04-04T20:18:03.055Z</t>
   </si>
   <si>
     <t>Intel Inside - Built for AI</t>
@@ -70,7 +70,7 @@
     <t>institutional-landing</t>
   </si>
   <si>
-    <t>2026-04-01T20:31:44.366Z</t>
+    <t>2026-04-04T20:12:21.769Z</t>
   </si>
   <si>
     <t>Intel Support</t>
@@ -127,7 +127,7 @@
     <t>artificial-intelligence/overview</t>
   </si>
   <si>
-    <t>2026-04-04T17:46:47.943Z</t>
+    <t>2026-04-04T20:18:13.525Z</t>
   </si>
   <si>
     <t>Explore Intel® Artificial Intelligence Solutions</t>
@@ -214,7 +214,7 @@
     <t>corporate-responsibility/corporate-responsibility</t>
   </si>
   <si>
-    <t>2026-04-01T20:31:49.007Z</t>
+    <t>2026-04-04T20:12:26.817Z</t>
   </si>
   <si>
     <t>Corporate Social Responsibility</t>
@@ -244,7 +244,7 @@
     <t>developer/overview</t>
   </si>
   <si>
-    <t>2026-04-01T20:26:18.055Z</t>
+    <t>2026-04-04T20:12:17.506Z</t>
   </si>
   <si>
     <t>Intel Developer Zone</t>
@@ -352,7 +352,7 @@
     <t>gaming/serious-gaming</t>
   </si>
   <si>
-    <t>2026-04-04T17:46:43.880Z</t>
+    <t>2026-04-04T20:18:07.242Z</t>
   </si>
   <si>
     <t>Next‑Gen Gaming PCs Powered by Intel® Core™ Ultra Series 2</t>
@@ -400,7 +400,7 @@
     <t>products/overview</t>
   </si>
   <si>
-    <t>2026-04-01T20:26:11.962Z</t>
+    <t>2026-04-04T20:12:11.668Z</t>
   </si>
   <si>
     <t>Intel® Core™ Processors, FPGAs, GPUs, Networking, Software</t>

--- a/tools/importer/reports/import-marketing-landing.report.xlsx
+++ b/tools/importer/reports/import-marketing-landing.report.xlsx
@@ -70,7 +70,7 @@
     <t>institutional-landing</t>
   </si>
   <si>
-    <t>2026-04-04T20:12:21.769Z</t>
+    <t>2026-04-04T20:18:26.098Z</t>
   </si>
   <si>
     <t>Intel Support</t>
@@ -91,7 +91,7 @@
     <t>marketing-landing</t>
   </si>
   <si>
-    <t>2026-04-03T20:58:16.627Z</t>
+    <t>2026-04-04T21:46:02.333Z</t>
   </si>
   <si>
     <t>The AI PC Powered by Intel. Now AI Is for Everyone</t>
@@ -214,7 +214,7 @@
     <t>corporate-responsibility/corporate-responsibility</t>
   </si>
   <si>
-    <t>2026-04-04T20:12:26.817Z</t>
+    <t>2026-04-04T20:18:30.478Z</t>
   </si>
   <si>
     <t>Corporate Social Responsibility</t>
@@ -244,7 +244,7 @@
     <t>developer/overview</t>
   </si>
   <si>
-    <t>2026-04-04T20:12:17.506Z</t>
+    <t>2026-04-04T20:18:21.897Z</t>
   </si>
   <si>
     <t>Intel Developer Zone</t>
@@ -298,7 +298,7 @@
     <t>gaming/esports</t>
   </si>
   <si>
-    <t>2026-04-03T20:58:09.629Z</t>
+    <t>2026-04-04T21:46:07.651Z</t>
   </si>
   <si>
     <t>Esports: Transforming the Future of Gaming Technology - Intel</t>
@@ -316,7 +316,7 @@
     <t>gaming/gaming-desktops</t>
   </si>
   <si>
-    <t>2026-04-03T20:57:56.946Z</t>
+    <t>2026-04-04T21:46:13.314Z</t>
   </si>
   <si>
     <t>Gaming Desktops Powered by Intel Core Ultra 200S Plus</t>
@@ -334,7 +334,7 @@
     <t>gaming/gaming-laptops</t>
   </si>
   <si>
-    <t>2026-04-03T20:58:02.540Z</t>
+    <t>2026-04-04T21:46:18.751Z</t>
   </si>
   <si>
     <t>Gaming Laptops Powered by Intel® Core Ultra Series 2</t>
@@ -400,7 +400,7 @@
     <t>products/overview</t>
   </si>
   <si>
-    <t>2026-04-04T20:12:11.668Z</t>
+    <t>2026-04-04T20:18:16.919Z</t>
   </si>
   <si>
     <t>Intel® Core™ Processors, FPGAs, GPUs, Networking, Software</t>

--- a/tools/importer/reports/import-marketing-landing.report.xlsx
+++ b/tools/importer/reports/import-marketing-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="190">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>ark.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>ark</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>category-directory</t>
+  </si>
+  <si>
+    <t>2026-04-05T11:50:08.226Z</t>
+  </si>
+  <si>
+    <t>Intel® Product Specifications</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/ark.html</t>
+  </si>
+  <si>
     <t>homepage.report.json</t>
   </si>
   <si>
@@ -46,9 +70,6 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>2026-04-04T20:18:03.055Z</t>
   </si>
   <si>
@@ -172,15 +193,9 @@
     <t>cloud-computing/overview.report.json</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
     <t>cloud-computing/overview</t>
   </si>
   <si>
-    <t>category-directory</t>
-  </si>
-  <si>
     <t>2026-04-03T21:00:06.719Z</t>
   </si>
   <si>
@@ -280,7 +295,7 @@
     <t>environment/sustainability</t>
   </si>
   <si>
-    <t>2026-04-03T20:58:58.658Z</t>
+    <t>2026-04-05T11:50:28.479Z</t>
   </si>
   <si>
     <t>Sustainable Computing for a Sustainable Future</t>
@@ -289,6 +304,24 @@
     <t>https://www.intel.com/content/www/us/en/environment/sustainability.html</t>
   </si>
   <si>
+    <t>foundry/overview.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","columns","columns"]</t>
+  </si>
+  <si>
+    <t>foundry/overview</t>
+  </si>
+  <si>
+    <t>2026-04-05T11:50:33.656Z</t>
+  </si>
+  <si>
+    <t>Semiconductor Manufacturing Company for the AI Era</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/foundry/overview.html</t>
+  </si>
+  <si>
     <t>gaming/esports.report.json</t>
   </si>
   <si>
@@ -394,6 +427,21 @@
     <t>https://www.intel.com/content/www/us/en/manufacturing/manufacturing-industrial-overview.html</t>
   </si>
   <si>
+    <t>partner-alliance/overview.report.json</t>
+  </si>
+  <si>
+    <t>partner-alliance/overview</t>
+  </si>
+  <si>
+    <t>2026-04-05T11:50:18.817Z</t>
+  </si>
+  <si>
+    <t>Intel® Partner Alliance</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/partner-alliance/overview.html</t>
+  </si>
+  <si>
     <t>products/overview.report.json</t>
   </si>
   <si>
@@ -412,10 +460,13 @@
     <t>security/overview.report.json</t>
   </si>
   <si>
+    <t>["hero","cards-product","cards-product","cards-product","cards-product","cards-product","cards-product","cards-product","columns"]</t>
+  </si>
+  <si>
     <t>security/overview</t>
   </si>
   <si>
-    <t>2026-04-03T21:00:17.973Z</t>
+    <t>2026-04-05T11:50:23.414Z</t>
   </si>
   <si>
     <t>Security Innovation for Business Networks | Intel®</t>
@@ -430,7 +481,7 @@
     <t>topics/overview</t>
   </si>
   <si>
-    <t>2026-04-03T21:00:01.146Z</t>
+    <t>2026-04-05T11:50:13.176Z</t>
   </si>
   <si>
     <t>Topics</t>
@@ -918,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -967,27 +1018,27 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1045,111 +1096,111 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
@@ -1166,7 +1217,7 @@
         <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
         <v>60</v>
@@ -1175,7 +1226,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
         <v>61</v>
@@ -1192,33 +1243,33 @@
         <v>64</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
         <v>65</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
         <v>66</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>67</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>68</v>
-      </c>
-      <c r="H11" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
         <v>70</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
       </c>
       <c r="C12" t="s">
         <v>71</v>
@@ -1227,7 +1278,7 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
         <v>72</v>
@@ -1244,7 +1295,7 @@
         <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
         <v>76</v>
@@ -1253,7 +1304,7 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
         <v>77</v>
@@ -1270,163 +1321,163 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
         <v>81</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
         <v>82</v>
       </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>83</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>84</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
         <v>86</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>87</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
         <v>88</v>
       </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>89</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>90</v>
-      </c>
-      <c r="H15" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
         <v>92</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>93</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" t="s">
         <v>94</v>
       </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>95</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>96</v>
-      </c>
-      <c r="H16" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" t="s">
         <v>98</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>99</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
         <v>100</v>
       </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>101</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>102</v>
-      </c>
-      <c r="H17" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" t="s">
         <v>104</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>105</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
         <v>106</v>
       </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>107</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>108</v>
-      </c>
-      <c r="H18" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s">
         <v>110</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>111</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
         <v>112</v>
       </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>113</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>114</v>
-      </c>
-      <c r="H19" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" t="s">
         <v>116</v>
-      </c>
-      <c r="B20" t="s">
-        <v>53</v>
       </c>
       <c r="C20" t="s">
         <v>117</v>
@@ -1435,7 +1486,7 @@
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
         <v>118</v>
@@ -1461,7 +1512,7 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
         <v>124</v>
@@ -1478,7 +1529,7 @@
         <v>127</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
         <v>128</v>
@@ -1487,7 +1538,7 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
         <v>129</v>
@@ -1504,207 +1555,285 @@
         <v>132</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H24" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G26" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G27" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G29" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H29" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s">
-        <v>168</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H30" t="s">
-        <v>172</v>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>175</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>176</v>
+      </c>
+      <c r="G31" t="s">
+        <v>177</v>
+      </c>
+      <c r="H31" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" t="s">
+        <v>181</v>
+      </c>
+      <c r="G32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H32" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F33" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H33" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-marketing-landing.report.xlsx
+++ b/tools/importer/reports/import-marketing-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="262">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>category-directory</t>
   </si>
   <si>
-    <t>2026-04-05T11:50:08.226Z</t>
+    <t>2026-04-05T16:31:53.358Z</t>
   </si>
   <si>
     <t>Intel® Product Specifications</t>
@@ -211,7 +211,7 @@
     <t>company-overview/company-overview</t>
   </si>
   <si>
-    <t>2026-04-03T21:01:07.254Z</t>
+    <t>2026-04-05T11:50:47.858Z</t>
   </si>
   <si>
     <t>Innovation starts here</t>
@@ -238,6 +238,21 @@
     <t>https://www.intel.com/content/www/us/en/corporate-responsibility/corporate-responsibility.html</t>
   </si>
   <si>
+    <t>customer-spotlight/overview.report.json</t>
+  </si>
+  <si>
+    <t>customer-spotlight/overview</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:18.639Z</t>
+  </si>
+  <si>
+    <t>Intel Customer Spotlight: Customer Stories and Case Studies</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/customer-spotlight/overview.html</t>
+  </si>
+  <si>
     <t>data-center/overview.report.json</t>
   </si>
   <si>
@@ -268,6 +283,21 @@
     <t>https://www.intel.com/content/www/us/en/developer/overview.html</t>
   </si>
   <si>
+    <t>download-center/home.report.json</t>
+  </si>
+  <si>
+    <t>download-center/home</t>
+  </si>
+  <si>
+    <t>2026-04-05T11:50:37.419Z</t>
+  </si>
+  <si>
+    <t>Download Intel Drivers and Software</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/download-center/home.html</t>
+  </si>
+  <si>
     <t>edge-computing/overview.report.json</t>
   </si>
   <si>
@@ -322,6 +352,57 @@
     <t>https://www.intel.com/content/www/us/en/foundry/overview.html</t>
   </si>
   <si>
+    <t>foundry/packaging.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","cards-product","cards-product","columns","columns","columns","columns","columns","columns","columns","columns","columns"]</t>
+  </si>
+  <si>
+    <t>foundry/packaging</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:51.807Z</t>
+  </si>
+  <si>
+    <t>Advanced Packaging Innovations | Chip Packages</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/foundry/packaging.html</t>
+  </si>
+  <si>
+    <t>foundry/process.report.json</t>
+  </si>
+  <si>
+    <t>["cards-product","cards-product","columns"]</t>
+  </si>
+  <si>
+    <t>foundry/process</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:47.312Z</t>
+  </si>
+  <si>
+    <t>Semiconductor Manufacturing Process | Intel 18A, 3, and 16</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/foundry/process.html</t>
+  </si>
+  <si>
+    <t>foundry/systems-foundry.report.json</t>
+  </si>
+  <si>
+    <t>foundry/systems-foundry</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:57.525Z</t>
+  </si>
+  <si>
+    <t>Semiconductor Manufacturing Systems Foundry for the AI Era</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/foundry/systems-foundry.html</t>
+  </si>
+  <si>
     <t>gaming/esports.report.json</t>
   </si>
   <si>
@@ -409,6 +490,39 @@
     <t>https://www.intel.com/content/www/us/en/high-performance-computing/overview.html</t>
   </si>
   <si>
+    <t>industries/overview.report.json</t>
+  </si>
+  <si>
+    <t>industries/overview</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:23.936Z</t>
+  </si>
+  <si>
+    <t>Industry 4.0 and Smart Manufacturing Technology Solutions Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/industries/overview.html</t>
+  </si>
+  <si>
+    <t>jobs/life-at-intel.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards-news"]</t>
+  </si>
+  <si>
+    <t>jobs/life-at-intel</t>
+  </si>
+  <si>
+    <t>2026-04-05T11:50:53.581Z</t>
+  </si>
+  <si>
+    <t>Work and Life at Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/jobs/life-at-intel.html</t>
+  </si>
+  <si>
     <t>manufacturing/manufacturing-industrial-overview.report.json</t>
   </si>
   <si>
@@ -421,9 +535,6 @@
     <t>2026-04-03T20:58:53.206Z</t>
   </si>
   <si>
-    <t>Industry 4.0 and Smart Manufacturing Technology Solutions Intel</t>
-  </si>
-  <si>
     <t>https://www.intel.com/content/www/us/en/manufacturing/manufacturing-industrial-overview.html</t>
   </si>
   <si>
@@ -433,7 +544,7 @@
     <t>partner-alliance/overview</t>
   </si>
   <si>
-    <t>2026-04-05T11:50:18.817Z</t>
+    <t>2026-04-05T16:55:38.134Z</t>
   </si>
   <si>
     <t>Intel® Partner Alliance</t>
@@ -457,6 +568,21 @@
     <t>https://www.intel.com/content/www/us/en/products/overview.html</t>
   </si>
   <si>
+    <t>products/systems-devices.report.json</t>
+  </si>
+  <si>
+    <t>products/systems-devices</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:41.631Z</t>
+  </si>
+  <si>
+    <t>Computer Systems and Devices Powered by Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/products/systems-devices.html</t>
+  </si>
+  <si>
     <t>security/overview.report.json</t>
   </si>
   <si>
@@ -475,6 +601,36 @@
     <t>https://www.intel.com/content/www/us/en/security/overview.html</t>
   </si>
   <si>
+    <t>software/software-overview.report.json</t>
+  </si>
+  <si>
+    <t>software/software-overview</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:29.279Z</t>
+  </si>
+  <si>
+    <t>Intel® Tiber™ Portfolio of Business Solutions</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/software/software-overview.html</t>
+  </si>
+  <si>
+    <t>support/detect.report.json</t>
+  </si>
+  <si>
+    <t>support/detect</t>
+  </si>
+  <si>
+    <t>2026-04-05T11:50:41.779Z</t>
+  </si>
+  <si>
+    <t>Intel® Driver &amp; Support Assistant</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/support/detect.html</t>
+  </si>
+  <si>
     <t>topics/overview.report.json</t>
   </si>
   <si>
@@ -490,6 +646,36 @@
     <t>https://www.intel.com/content/www/us/en/topics/overview.html</t>
   </si>
   <si>
+    <t>developer/community/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/community/overview</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:05.136Z</t>
+  </si>
+  <si>
+    <t>Community &amp; Events</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/community/overview.html</t>
+  </si>
+  <si>
+    <t>developer/learn/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/learn/overview</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:00.344Z</t>
+  </si>
+  <si>
+    <t>Developer Training</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/learn/overview.html</t>
+  </si>
+  <si>
     <t>developer/programs/overview.report.json</t>
   </si>
   <si>
@@ -511,7 +697,7 @@
     <t>developer/tools/overview</t>
   </si>
   <si>
-    <t>2026-04-03T20:59:51.171Z</t>
+    <t>2026-04-05T19:08:56.098Z</t>
   </si>
   <si>
     <t>Development Tools</t>
@@ -548,6 +734,36 @@
   </si>
   <si>
     <t>https://www.intel.com/content/www/us/en/gaming/resources/overview.html</t>
+  </si>
+  <si>
+    <t>products/details/processors.report.json</t>
+  </si>
+  <si>
+    <t>products/details/processors</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:36.120Z</t>
+  </si>
+  <si>
+    <t>Intel® Processors – Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/products/details/processors.html</t>
+  </si>
+  <si>
+    <t>developer/tools/software-catalog/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/tools/software-catalog/overview</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:09:11.380Z</t>
+  </si>
+  <si>
+    <t>Intel® Developer Catalog</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/tools/software-catalog/overview.html</t>
   </si>
   <si>
     <t>products/details/processors/core-ultra.report.json</t>
@@ -969,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -1347,62 +1563,62 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
         <v>86</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
         <v>87</v>
       </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>88</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>89</v>
-      </c>
-      <c r="H15" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
         <v>91</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
         <v>92</v>
       </c>
-      <c r="C16" t="s">
+      <c r="G16" t="s">
         <v>93</v>
       </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>94</v>
-      </c>
-      <c r="G16" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
         <v>97</v>
-      </c>
-      <c r="B17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" t="s">
-        <v>99</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -1411,24 +1627,24 @@
         <v>32</v>
       </c>
       <c r="F17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" t="s">
         <v>100</v>
-      </c>
-      <c r="G17" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
         <v>103</v>
-      </c>
-      <c r="B18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" t="s">
-        <v>105</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -1437,24 +1653,24 @@
         <v>32</v>
       </c>
       <c r="F18" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" t="s">
         <v>106</v>
-      </c>
-      <c r="G18" t="s">
-        <v>107</v>
-      </c>
-      <c r="H18" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
         <v>109</v>
-      </c>
-      <c r="B19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -1463,24 +1679,24 @@
         <v>32</v>
       </c>
       <c r="F19" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" t="s">
         <v>112</v>
-      </c>
-      <c r="G19" t="s">
-        <v>113</v>
-      </c>
-      <c r="H19" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" t="s">
         <v>115</v>
-      </c>
-      <c r="B20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" t="s">
-        <v>117</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -1489,24 +1705,24 @@
         <v>32</v>
       </c>
       <c r="F20" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H20" t="s">
         <v>118</v>
-      </c>
-      <c r="G20" t="s">
-        <v>119</v>
-      </c>
-      <c r="H20" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" t="s">
         <v>121</v>
-      </c>
-      <c r="B21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" t="s">
-        <v>123</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -1515,50 +1731,50 @@
         <v>32</v>
       </c>
       <c r="F21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" t="s">
         <v>124</v>
-      </c>
-      <c r="G21" t="s">
-        <v>125</v>
-      </c>
-      <c r="H21" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
         <v>127</v>
       </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="G22" t="s">
         <v>128</v>
       </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
         <v>129</v>
-      </c>
-      <c r="G22" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" t="s">
         <v>132</v>
-      </c>
-      <c r="B23" t="s">
-        <v>133</v>
-      </c>
-      <c r="C23" t="s">
-        <v>134</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1567,47 +1783,47 @@
         <v>32</v>
       </c>
       <c r="F23" t="s">
+        <v>133</v>
+      </c>
+      <c r="G23" t="s">
+        <v>134</v>
+      </c>
+      <c r="H23" t="s">
         <v>135</v>
-      </c>
-      <c r="G23" t="s">
-        <v>136</v>
-      </c>
-      <c r="H23" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" t="s">
         <v>138</v>
       </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
         <v>139</v>
       </c>
-      <c r="D24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>140</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>141</v>
-      </c>
-      <c r="H24" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" t="s">
         <v>143</v>
-      </c>
-      <c r="B25" t="s">
-        <v>104</v>
       </c>
       <c r="C25" t="s">
         <v>144</v>
@@ -1616,7 +1832,7 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
         <v>145</v>
@@ -1711,62 +1927,62 @@
         <v>164</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>165</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="C30" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G30" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="H30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -1775,47 +1991,47 @@
         <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G32" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s">
-        <v>185</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
         <v>186</v>
@@ -1824,7 +2040,7 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F33" t="s">
         <v>187</v>
@@ -1834,6 +2050,370 @@
       </c>
       <c r="H33" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" t="s">
+        <v>192</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" t="s">
+        <v>193</v>
+      </c>
+      <c r="G34" t="s">
+        <v>194</v>
+      </c>
+      <c r="H34" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>197</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>198</v>
+      </c>
+      <c r="G35" t="s">
+        <v>199</v>
+      </c>
+      <c r="H35" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>203</v>
+      </c>
+      <c r="G36" t="s">
+        <v>204</v>
+      </c>
+      <c r="H36" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>206</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s">
+        <v>207</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" t="s">
+        <v>208</v>
+      </c>
+      <c r="G37" t="s">
+        <v>209</v>
+      </c>
+      <c r="H37" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>211</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s">
+        <v>212</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>213</v>
+      </c>
+      <c r="G38" t="s">
+        <v>214</v>
+      </c>
+      <c r="H38" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>216</v>
+      </c>
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s">
+        <v>217</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>218</v>
+      </c>
+      <c r="G39" t="s">
+        <v>219</v>
+      </c>
+      <c r="H39" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>221</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>223</v>
+      </c>
+      <c r="G40" t="s">
+        <v>224</v>
+      </c>
+      <c r="H40" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>226</v>
+      </c>
+      <c r="B41" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
+        <v>227</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>228</v>
+      </c>
+      <c r="G41" t="s">
+        <v>229</v>
+      </c>
+      <c r="H41" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>231</v>
+      </c>
+      <c r="B42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>232</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
+        <v>233</v>
+      </c>
+      <c r="G42" t="s">
+        <v>234</v>
+      </c>
+      <c r="H42" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>236</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s">
+        <v>237</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" t="s">
+        <v>238</v>
+      </c>
+      <c r="G43" t="s">
+        <v>239</v>
+      </c>
+      <c r="H43" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>241</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
+        <v>242</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>243</v>
+      </c>
+      <c r="G44" t="s">
+        <v>244</v>
+      </c>
+      <c r="H44" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>246</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s">
+        <v>247</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>248</v>
+      </c>
+      <c r="G45" t="s">
+        <v>249</v>
+      </c>
+      <c r="H45" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>251</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" t="s">
+        <v>252</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>32</v>
+      </c>
+      <c r="F46" t="s">
+        <v>253</v>
+      </c>
+      <c r="G46" t="s">
+        <v>254</v>
+      </c>
+      <c r="H46" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>256</v>
+      </c>
+      <c r="B47" t="s">
+        <v>257</v>
+      </c>
+      <c r="C47" t="s">
+        <v>258</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
+        <v>259</v>
+      </c>
+      <c r="G47" t="s">
+        <v>260</v>
+      </c>
+      <c r="H47" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-marketing-landing.report.xlsx
+++ b/tools/importer/reports/import-marketing-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="277">
   <si>
     <t>_reportFile</t>
   </si>
@@ -361,7 +361,7 @@
     <t>foundry/packaging</t>
   </si>
   <si>
-    <t>2026-04-05T19:09:51.807Z</t>
+    <t>2026-04-06T02:16:52.899Z</t>
   </si>
   <si>
     <t>Advanced Packaging Innovations | Chip Packages</t>
@@ -379,7 +379,7 @@
     <t>foundry/process</t>
   </si>
   <si>
-    <t>2026-04-05T19:09:47.312Z</t>
+    <t>2026-04-06T02:16:47.617Z</t>
   </si>
   <si>
     <t>Semiconductor Manufacturing Process | Intel 18A, 3, and 16</t>
@@ -394,7 +394,7 @@
     <t>foundry/systems-foundry</t>
   </si>
   <si>
-    <t>2026-04-05T19:09:57.525Z</t>
+    <t>2026-04-06T02:16:57.776Z</t>
   </si>
   <si>
     <t>Semiconductor Manufacturing Systems Foundry for the AI Era</t>
@@ -490,6 +490,21 @@
     <t>https://www.intel.com/content/www/us/en/high-performance-computing/overview.html</t>
   </si>
   <si>
+    <t>inclusion/inclusion-at-intel.report.json</t>
+  </si>
+  <si>
+    <t>inclusion/inclusion-at-intel</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:10:07.240Z</t>
+  </si>
+  <si>
+    <t>Inclusion at Intel</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/inclusion/inclusion-at-intel.html</t>
+  </si>
+  <si>
     <t>industries/overview.report.json</t>
   </si>
   <si>
@@ -514,7 +529,7 @@
     <t>jobs/life-at-intel</t>
   </si>
   <si>
-    <t>2026-04-05T11:50:53.581Z</t>
+    <t>2026-04-06T00:38:31.863Z</t>
   </si>
   <si>
     <t>Work and Life at Intel</t>
@@ -652,7 +667,7 @@
     <t>developer/community/overview</t>
   </si>
   <si>
-    <t>2026-04-05T19:09:05.136Z</t>
+    <t>2026-04-06T02:15:55.965Z</t>
   </si>
   <si>
     <t>Community &amp; Events</t>
@@ -661,13 +676,28 @@
     <t>https://www.intel.com/content/www/us/en/developer/community/overview.html</t>
   </si>
   <si>
+    <t>developer/get-help/overview.report.json</t>
+  </si>
+  <si>
+    <t>developer/get-help/overview</t>
+  </si>
+  <si>
+    <t>2026-04-06T02:16:02.437Z</t>
+  </si>
+  <si>
+    <t>Intel® Product Support</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/developer/get-help/overview.html</t>
+  </si>
+  <si>
     <t>developer/learn/overview.report.json</t>
   </si>
   <si>
     <t>developer/learn/overview</t>
   </si>
   <si>
-    <t>2026-04-05T19:09:00.344Z</t>
+    <t>2026-04-06T02:15:49.219Z</t>
   </si>
   <si>
     <t>Developer Training</t>
@@ -697,7 +727,7 @@
     <t>developer/tools/overview</t>
   </si>
   <si>
-    <t>2026-04-05T19:08:56.098Z</t>
+    <t>2026-04-06T02:15:44.474Z</t>
   </si>
   <si>
     <t>Development Tools</t>
@@ -736,6 +766,21 @@
     <t>https://www.intel.com/content/www/us/en/gaming/resources/overview.html</t>
   </si>
   <si>
+    <t>partner-alliance/membership/overview.report.json</t>
+  </si>
+  <si>
+    <t>partner-alliance/membership/overview</t>
+  </si>
+  <si>
+    <t>2026-04-05T19:10:12.791Z</t>
+  </si>
+  <si>
+    <t>Intel® Partner Alliance Membership Benefits</t>
+  </si>
+  <si>
+    <t>https://www.intel.com/content/www/us/en/partner-alliance/membership/overview.html</t>
+  </si>
+  <si>
     <t>products/details/processors.report.json</t>
   </si>
   <si>
@@ -757,7 +802,7 @@
     <t>developer/tools/software-catalog/overview</t>
   </si>
   <si>
-    <t>2026-04-05T19:09:11.380Z</t>
+    <t>2026-04-06T02:16:08.077Z</t>
   </si>
   <si>
     <t>Intel® Developer Catalog</t>
@@ -1185,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -1910,7 +1955,7 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F28" t="s">
         <v>161</v>
@@ -1927,48 +1972,48 @@
         <v>164</v>
       </c>
       <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
         <v>165</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
         <v>166</v>
       </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>167</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>168</v>
-      </c>
-      <c r="H29" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" t="s">
         <v>170</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>171</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
         <v>172</v>
       </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>173</v>
-      </c>
-      <c r="G30" t="s">
-        <v>162</v>
       </c>
       <c r="H30" t="s">
         <v>174</v>
@@ -1979,22 +2024,22 @@
         <v>175</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G31" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="H31" t="s">
         <v>179</v>
@@ -2005,7 +2050,7 @@
         <v>180</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
         <v>181</v>
@@ -2031,7 +2076,7 @@
         <v>185</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s">
         <v>186</v>
@@ -2057,33 +2102,33 @@
         <v>190</v>
       </c>
       <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
         <v>191</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
         <v>192</v>
       </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>193</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>194</v>
-      </c>
-      <c r="H34" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>195</v>
+      </c>
+      <c r="B35" t="s">
         <v>196</v>
-      </c>
-      <c r="B35" t="s">
-        <v>9</v>
       </c>
       <c r="C35" t="s">
         <v>197</v>
@@ -2092,7 +2137,7 @@
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F35" t="s">
         <v>198</v>
@@ -2118,7 +2163,7 @@
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F36" t="s">
         <v>203</v>
@@ -2144,7 +2189,7 @@
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F37" t="s">
         <v>208</v>
@@ -2369,7 +2414,7 @@
         <v>251</v>
       </c>
       <c r="B46" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C46" t="s">
         <v>252</v>
@@ -2378,7 +2423,7 @@
         <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F46" t="s">
         <v>253</v>
@@ -2395,25 +2440,103 @@
         <v>256</v>
       </c>
       <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" t="s">
         <v>257</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
         <v>258</v>
       </c>
-      <c r="D47" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
+        <v>259</v>
+      </c>
+      <c r="H47" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>261</v>
+      </c>
+      <c r="B48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" t="s">
+        <v>262</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
+        <v>263</v>
+      </c>
+      <c r="G48" t="s">
+        <v>264</v>
+      </c>
+      <c r="H48" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>266</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" t="s">
+        <v>267</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
         <v>32</v>
       </c>
-      <c r="F47" t="s">
-        <v>259</v>
-      </c>
-      <c r="G47" t="s">
-        <v>260</v>
-      </c>
-      <c r="H47" t="s">
-        <v>261</v>
+      <c r="F49" t="s">
+        <v>268</v>
+      </c>
+      <c r="G49" t="s">
+        <v>269</v>
+      </c>
+      <c r="H49" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>271</v>
+      </c>
+      <c r="B50" t="s">
+        <v>272</v>
+      </c>
+      <c r="C50" t="s">
+        <v>273</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" t="s">
+        <v>274</v>
+      </c>
+      <c r="G50" t="s">
+        <v>275</v>
+      </c>
+      <c r="H50" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
